--- a/HD-02_需求追溯矩阵.xlsx
+++ b/HD-02_需求追溯矩阵.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +47,13 @@
     </font>
     <font>
       <color rgb="00111827"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
       <sz val="9.5"/>
     </font>
   </fonts>
@@ -89,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -108,6 +115,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -475,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -553,6 +567,69 @@
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>注意：⑤ 类条款保留在表中而未删除，原因是投标阶段的责任划分可能被总包商调整；一旦调整，这些条款会重新落入我方范围，届时需要有历史依据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>【2026-09 补充】新增「对应 LD 册与章节」列</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>详细设计十一册成文后，本表补上从需求到详细设计的下半段追溯。「需求清单」页新增两列，「追溯矩阵」页新增一列。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>映射依据分三级，写在「映射依据」列里，不混为一谈：</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>一、LD 正文显式引用——该册正文或表格中直接出现了该需求编号，章节号即引用所在章。证据最强，共 19 条。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>二、领域主章——按需求的领域代码映射到对应册的主章节。章号已逐一对照各册实际标题核实，不是按印象填的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>三、责任组件——「另涉 …」部分由需求清单的责任组件列（L1 至 L6）推出，只到册一级，不给章节号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>「追溯矩阵」页只给到册一级：该页一行对应一条 RFP 条款，可能牵涉多条需求，给章节号会失真。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>覆盖方式为「领域覆盖」的 72 行按其领域代码映射，标注「（领域覆盖）」以区别于逐条映射。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>本次同时更正：「需人工复核的条款」页引用的 M-I09 在 metrics.yaml 中已不存在——LD-03 把处置时长拆为均值、中位、P90 三个指标，已改为 M-I06 · M-I22 · M-I23。</t>
         </is>
       </c>
     </row>
@@ -567,7 +644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I190"/>
+  <dimension ref="A1:J190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -579,6 +656,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -627,6 +705,11 @@
           <t>开发状态</t>
         </is>
       </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>对应 LD 册</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -670,6 +753,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-03</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -713,6 +801,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-03</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -760,6 +853,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-02 · LD-03 · LD-04</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -803,6 +901,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-03 · LD-04 · LD-08</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -846,6 +949,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-03 · LD-04</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -889,6 +997,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-03 · LD-04</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -932,6 +1045,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-06 · LD-08</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -975,6 +1093,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-06 · LD-08</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1018,6 +1141,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-04</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1061,6 +1189,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-04 · LD-05</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1108,6 +1241,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-05</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1151,6 +1289,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-05</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1194,6 +1337,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-05</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1237,6 +1385,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-05</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1280,6 +1433,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-05</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1323,6 +1481,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1364,6 +1527,11 @@
       <c r="I18" s="5" t="inlineStr">
         <is>
           <t>待开发</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-04 · LD-05 · LD-06</t>
         </is>
       </c>
     </row>
@@ -1405,6 +1573,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-05 · LD-05A（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1444,6 +1617,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-05 · LD-05A（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1485,6 +1663,11 @@
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>待开发</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>LD-03 · LD-05 · LD-05A</t>
         </is>
       </c>
     </row>
@@ -1526,6 +1709,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-05 · LD-05A（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1569,6 +1757,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-03</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1612,6 +1805,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-03 · LD-05</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1659,6 +1857,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1702,6 +1905,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-03 · LD-04 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1749,6 +1957,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-03 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1792,6 +2005,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-03 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1835,6 +2053,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-03 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -1878,6 +2101,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-03 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1921,6 +2149,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-03 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1964,6 +2197,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-03 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2007,6 +2245,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-06</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -2050,6 +2293,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J34" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -2093,6 +2341,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -2136,6 +2389,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -2179,6 +2437,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2222,6 +2485,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -2269,6 +2537,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -2310,6 +2583,11 @@
       <c r="I40" s="5" t="inlineStr">
         <is>
           <t>待开发</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 · LD-05A</t>
         </is>
       </c>
     </row>
@@ -2351,6 +2629,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-05 · LD-05A（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2394,6 +2677,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J42" s="7" t="inlineStr">
+        <is>
+          <t>LD-03 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -2437,6 +2725,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>LD-03 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -2480,6 +2773,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J44" s="7" t="inlineStr">
+        <is>
+          <t>LD-03 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -2523,6 +2821,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -2570,6 +2873,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J46" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -2617,6 +2925,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -2664,6 +2977,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-04</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -2711,6 +3029,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-02 · LD-03 · LD-04 · LD-05 · LD-05A · LD-06 · LD-07 · LD-08</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -2758,6 +3081,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -2805,6 +3133,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -2848,6 +3181,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>LD-00 · LD-02</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -2891,6 +3229,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>LD-00 · LD-02</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -2934,6 +3277,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>LD-00 · LD-05</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -2977,6 +3325,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>LD-00 · LD-02 · LD-05</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -3020,6 +3373,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>LD-00 · LD-02 · LD-03 · LD-05 · LD-05A</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -3063,6 +3421,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>LD-00</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -3106,6 +3469,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J58" s="7" t="inlineStr">
+        <is>
+          <t>LD-00 · LD-04</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -3149,6 +3517,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>LD-00 · LD-02 · LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -3196,6 +3569,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>LD-01</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -3239,6 +3617,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>LD-01</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -3282,6 +3665,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>LD-01</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -3325,6 +3713,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-02</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -3368,6 +3761,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-03</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -3411,6 +3809,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>LD-01</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -3454,6 +3857,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>LD-01</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -3497,6 +3905,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-03</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -3544,6 +3957,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J68" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-03 · LD-10</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -3591,6 +4009,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-03</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -3634,6 +4057,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-10</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -3677,6 +4105,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>LD-01</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -3724,6 +4157,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-02 · LD-03 · LD-04</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -3767,6 +4205,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-07</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -3814,6 +4257,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-02 · LD-03 · LD-04 · LD-05 · LD-06 · LD-07 · LD-08</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -3857,6 +4305,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>LD-03 · LD-06 · LD-07</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -3900,6 +4353,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>LD-03 · LD-06 · LD-07</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -3947,6 +4405,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-06 · LD-07 · LD-08 · LD-10</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -3990,6 +4453,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-03 · LD-06 · LD-07</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -4037,6 +4505,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-04 · LD-05 · LD-06 · LD-08</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -4080,6 +4553,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-04 · LD-05 · LD-06 · LD-08</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -4123,6 +4601,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-04 · LD-05 · LD-06 · LD-08</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -4166,6 +4649,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J82" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-04 · LD-05 · LD-06 · LD-08</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -4209,6 +4697,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-04 · LD-05 · LD-06 · LD-08</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -4252,6 +4745,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J84" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-04 · LD-05 · LD-06 · LD-08</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -4295,6 +4793,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-05 · LD-10</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -4338,6 +4841,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-05 · LD-10</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -4381,6 +4889,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>LD-03 · LD-04 · LD-05 · LD-06</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -4424,6 +4937,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J88" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-04 · LD-05</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -4471,6 +4989,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-04 · LD-05</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -4514,6 +5037,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J90" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-04 · LD-05</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -4557,6 +5085,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-04 · LD-05</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -4604,6 +5137,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J92" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-05</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -4651,6 +5189,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-06 · LD-08 · LD-10</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -4694,6 +5237,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J94" s="7" t="inlineStr">
+        <is>
+          <t>LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -4737,6 +5285,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -4780,6 +5333,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J96" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -4827,6 +5385,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-04 · LD-05 · LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -4870,6 +5433,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J98" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -4917,6 +5485,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -4960,6 +5533,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J100" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -5003,6 +5581,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J101" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -5046,6 +5629,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J102" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -5089,6 +5677,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J103" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -5132,6 +5725,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J104" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -5175,6 +5773,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J105" s="7" t="inlineStr">
+        <is>
+          <t>LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -5218,6 +5821,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J106" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -5261,6 +5869,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J107" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08 · LD-09</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -5304,6 +5917,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J108" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-02 · LD-04</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -5345,6 +5963,11 @@
       <c r="I109" s="5" t="inlineStr">
         <is>
           <t>待开发</t>
+        </is>
+      </c>
+      <c r="J109" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-06</t>
         </is>
       </c>
     </row>
@@ -5386,6 +6009,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J110" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -5425,6 +6053,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J111" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -5464,6 +6097,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J112" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -5503,6 +6141,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J113" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -5542,6 +6185,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J114" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -5581,6 +6229,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J115" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -5624,6 +6277,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J116" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -5665,6 +6323,11 @@
       <c r="I117" s="5" t="inlineStr">
         <is>
           <t>待开发</t>
+        </is>
+      </c>
+      <c r="J117" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
         </is>
       </c>
     </row>
@@ -5706,6 +6369,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J118" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -5745,6 +6413,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J119" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -5784,6 +6457,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J120" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -5823,6 +6501,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J121" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -5862,6 +6545,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J122" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -5901,6 +6589,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J123" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -5940,6 +6633,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J124" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -5979,6 +6677,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J125" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
@@ -6018,6 +6721,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J126" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
@@ -6057,6 +6765,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J127" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
@@ -6096,6 +6809,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J128" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
@@ -6135,6 +6853,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J129" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
@@ -6180,6 +6903,11 @@
       <c r="I130" s="5" t="inlineStr">
         <is>
           <t>待开发</t>
+        </is>
+      </c>
+      <c r="J130" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-03</t>
         </is>
       </c>
     </row>
@@ -6221,6 +6949,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
@@ -6260,6 +6993,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J132" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
@@ -6307,6 +7045,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J133" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-03</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
@@ -6352,6 +7095,11 @@
       <c r="I134" s="5" t="inlineStr">
         <is>
           <t>待开发</t>
+        </is>
+      </c>
+      <c r="J134" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-03</t>
         </is>
       </c>
     </row>
@@ -6393,6 +7141,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J135" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
@@ -6432,6 +7185,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J136" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
@@ -6471,6 +7229,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J137" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
@@ -6510,6 +7273,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J138" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
@@ -6549,6 +7317,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J139" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
@@ -6588,6 +7361,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J140" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
@@ -6629,6 +7407,11 @@
       <c r="I141" s="5" t="inlineStr">
         <is>
           <t>待开发</t>
+        </is>
+      </c>
+      <c r="J141" s="7" t="inlineStr">
+        <is>
+          <t>LD-04</t>
         </is>
       </c>
     </row>
@@ -6670,6 +7453,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J142" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-05 · LD-05A（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
@@ -6713,6 +7501,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J143" s="7" t="inlineStr">
+        <is>
+          <t>LD-04</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
@@ -6758,6 +7551,11 @@
       <c r="I144" s="5" t="inlineStr">
         <is>
           <t>待开发</t>
+        </is>
+      </c>
+      <c r="J144" s="7" t="inlineStr">
+        <is>
+          <t>LD-04</t>
         </is>
       </c>
     </row>
@@ -6799,6 +7597,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J145" s="7" t="inlineStr">
+        <is>
+          <t>LD-02（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
@@ -6838,6 +7641,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J146" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-07（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
@@ -6877,6 +7685,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J147" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-07（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
@@ -6916,6 +7729,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J148" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-07（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
@@ -6955,6 +7773,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J149" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-07（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
@@ -7000,6 +7823,11 @@
       <c r="I150" s="5" t="inlineStr">
         <is>
           <t>待开发</t>
+        </is>
+      </c>
+      <c r="J150" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-07</t>
         </is>
       </c>
     </row>
@@ -7041,6 +7869,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J151" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-07（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
@@ -7080,6 +7913,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J152" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-07（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
@@ -7119,6 +7957,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J153" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-07（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
@@ -7158,6 +8001,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J154" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-07（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
@@ -7197,6 +8045,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J155" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 · LD-04（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
@@ -7240,6 +8093,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J156" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
@@ -7283,6 +8141,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J157" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-06 · LD-08</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
@@ -7326,6 +8189,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J158" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 · LD-05A · LD-06 · LD-08</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
@@ -7369,6 +8237,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J159" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 · LD-05 · LD-05A · LD-06 · LD-08</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
@@ -7416,6 +8289,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J160" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 · LD-06 · LD-08 · LD-10</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
@@ -7457,6 +8335,11 @@
       <c r="I161" s="5" t="inlineStr">
         <is>
           <t>待开发</t>
+        </is>
+      </c>
+      <c r="J161" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08</t>
         </is>
       </c>
     </row>
@@ -7498,6 +8381,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J162" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="5" t="inlineStr">
@@ -7537,6 +8425,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J163" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="5" t="inlineStr">
@@ -7576,6 +8469,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J164" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="5" t="inlineStr">
@@ -7615,6 +8513,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J165" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="inlineStr">
@@ -7654,6 +8557,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J166" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
@@ -7693,6 +8601,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J167" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
@@ -7732,6 +8645,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J168" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="5" t="inlineStr">
@@ -7771,6 +8689,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J169" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
@@ -7810,6 +8733,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J170" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
@@ -7849,6 +8777,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J171" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -7888,6 +8821,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J172" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="5" t="inlineStr">
@@ -7927,6 +8865,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J173" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
@@ -7966,6 +8909,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J174" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
@@ -8005,6 +8953,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J175" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
@@ -8044,6 +8997,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J176" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
@@ -8083,6 +9041,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J177" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
@@ -8122,6 +9085,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J178" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 · LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
@@ -8161,6 +9129,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J179" s="7" t="inlineStr">
+        <is>
+          <t>LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
@@ -8200,6 +9173,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J180" s="7" t="inlineStr">
+        <is>
+          <t>LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
@@ -8239,6 +9217,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J181" s="7" t="inlineStr">
+        <is>
+          <t>LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
@@ -8278,6 +9261,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J182" s="7" t="inlineStr">
+        <is>
+          <t>LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
@@ -8317,6 +9305,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J183" s="7" t="inlineStr">
+        <is>
+          <t>LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
@@ -8356,6 +9349,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J184" s="7" t="inlineStr">
+        <is>
+          <t>LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
@@ -8395,6 +9393,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J185" s="7" t="inlineStr">
+        <is>
+          <t>LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
@@ -8434,6 +9437,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J186" s="7" t="inlineStr">
+        <is>
+          <t>LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
@@ -8473,6 +9481,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J187" s="7" t="inlineStr">
+        <is>
+          <t>LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -8512,6 +9525,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J188" s="7" t="inlineStr">
+        <is>
+          <t>LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
@@ -8551,6 +9569,11 @@
           <t>待开发</t>
         </is>
       </c>
+      <c r="J189" s="7" t="inlineStr">
+        <is>
+          <t>LD-08（领域覆盖）</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
@@ -8588,6 +9611,11 @@
       <c r="I190" s="5" t="inlineStr">
         <is>
           <t>待开发</t>
+        </is>
+      </c>
+      <c r="J190" s="7" t="inlineStr">
+        <is>
+          <t>LD-08（领域覆盖）</t>
         </is>
       </c>
     </row>
@@ -8603,7 +9631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L125"/>
+  <dimension ref="A1:N125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8618,6 +9646,8 @@
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8681,6 +9711,16 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="M1" s="8" t="inlineStr">
+        <is>
+          <t>对应 LD 册与章节</t>
+        </is>
+      </c>
+      <c r="N1" s="8" t="inlineStr">
+        <is>
+          <t>映射依据</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -8739,6 +9779,16 @@
           <t>v0.2 修订：CN-01 由「RFP 强制」降为「RFP 要求（解读）」；列存加速层预设形态与触发条件见 DD-31</t>
         </is>
       </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 2 业务对象模型 · 9 raw 与 staging · 11 meta 与 audit</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -8793,6 +9843,16 @@
       </c>
       <c r="K3" s="5" t="inlineStr"/>
       <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 2 业务对象模型 · 9 raw 与 staging · 11 meta 与 audit ｜ 另涉 LD-03 · LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -8847,6 +9907,16 @@
       </c>
       <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 2 业务对象模型 · 9 raw 与 staging · 11 meta 与 audit ｜ 另涉 LD-06 · LD-08（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -8905,6 +9975,16 @@
           <t>v0.2 修订：实现组件指向 REQ-QRY-08（DD-34）</t>
         </is>
       </c>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 2 业务对象模型 · 9 raw 与 staging · 11 meta 与 audit ｜ 另涉 LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -8959,6 +10039,16 @@
       </c>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 2 业务对象模型 · 9 raw 与 staging · 11 meta 与 audit ｜ 另涉 LD-01（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -9013,6 +10103,16 @@
       </c>
       <c r="K7" s="5" t="inlineStr"/>
       <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 2 业务对象模型 · 9 raw 与 staging · 11 meta 与 audit ｜ 正文引用：LD-02 14 ; LD-04 12</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -9067,6 +10167,16 @@
       </c>
       <c r="K8" s="5" t="inlineStr"/>
       <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 2 源契约 · 3 增量接入 · 4 轮询接入 · 5 文件接入 · 7 校验隔离与放行 · 10 运行与观测</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -9121,6 +10231,16 @@
       </c>
       <c r="K9" s="5" t="inlineStr"/>
       <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 2 源契约 · 3 增量接入 · 4 轮询接入 · 5 文件接入 · 7 校验隔离与放行 · 10 运行与观测 ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -9175,6 +10295,16 @@
       </c>
       <c r="K10" s="5" t="inlineStr"/>
       <c r="L10" s="5" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 2 源契约 · 3 增量接入 · 4 轮询接入 · 5 文件接入 · 7 校验隔离与放行 · 10 运行与观测 ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -9229,6 +10359,16 @@
       </c>
       <c r="K11" s="5" t="inlineStr"/>
       <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 2 源契约 · 3 增量接入 · 4 轮询接入 · 5 文件接入 · 7 校验隔离与放行 · 10 运行与观测 ｜ 另涉 LD-03 · LD-05（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -9283,6 +10423,16 @@
       </c>
       <c r="K12" s="5" t="inlineStr"/>
       <c r="L12" s="5" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 2 源契约 · 3 增量接入 · 4 轮询接入 · 5 文件接入 · 7 校验隔离与放行 · 10 运行与观测</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -9337,6 +10487,16 @@
       </c>
       <c r="K13" s="5" t="inlineStr"/>
       <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 2 源契约 · 3 增量接入 · 4 轮询接入 · 5 文件接入 · 7 校验隔离与放行 · 10 运行与观测</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -9391,6 +10551,16 @@
       </c>
       <c r="K14" s="5" t="inlineStr"/>
       <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 2 源契约 · 3 增量接入 · 4 轮询接入 · 5 文件接入 · 7 校验隔离与放行 · 10 运行与观测 ｜ 另涉 LD-03 · LD-06（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -9449,6 +10619,16 @@
           <t>v0.2 修订：按取不到升级记录设计，跨版本值剖析反推版本边界（DD-37）</t>
         </is>
       </c>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 2 源契约 · 3 增量接入 · 4 轮询接入 · 5 文件接入 · 7 校验隔离与放行 · 10 运行与观测 ｜ 正文引用：LD-10 5.2 ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -9503,6 +10683,16 @@
       </c>
       <c r="K16" s="5" t="inlineStr"/>
       <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 6 归档迁移 · 8 对账</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -9561,6 +10751,16 @@
           <t>v0.2 修订：对账口径为记录数与关键字段逐条一致，未澄清字段原样保留（DD-37）</t>
         </is>
       </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 6 归档迁移 · 8 对账 ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -9615,6 +10815,16 @@
       </c>
       <c r="K18" s="5" t="inlineStr"/>
       <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 6 归档迁移 · 8 对账 ｜ 另涉 LD-03 · LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -9669,6 +10879,16 @@
       </c>
       <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 6 归档迁移 · 8 对账</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -9723,6 +10943,16 @@
       </c>
       <c r="K20" s="5" t="inlineStr"/>
       <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 3 粒度 · 4 代理键 · 5 分区主键 · 7 缓变维 · 12 索引与检索路径</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -9777,6 +11007,16 @@
       </c>
       <c r="K21" s="5" t="inlineStr"/>
       <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 3 粒度 · 4 代理键 · 5 分区主键 · 7 缓变维 · 12 索引与检索路径 ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -9831,6 +11071,16 @@
       </c>
       <c r="K22" s="5" t="inlineStr"/>
       <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 3 粒度 · 4 代理键 · 5 分区主键 · 7 缓变维 · 12 索引与检索路径 ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -9885,6 +11135,16 @@
       </c>
       <c r="K23" s="5" t="inlineStr"/>
       <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 3 粒度 · 4 代理键 · 5 分区主键 · 7 缓变维 · 12 索引与检索路径 ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -9939,6 +11199,16 @@
       </c>
       <c r="K24" s="5" t="inlineStr"/>
       <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 3 粒度 · 4 代理键 · 5 分区主键 · 7 缓变维 · 12 索引与检索路径 ｜ 正文引用：LD-02 14 ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -9993,6 +11263,16 @@
       </c>
       <c r="K25" s="5" t="inlineStr"/>
       <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 3 粒度 · 4 代理键 · 5 分区主键 · 7 缓变维 · 12 索引与检索路径</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -10047,6 +11327,16 @@
       </c>
       <c r="K26" s="5" t="inlineStr"/>
       <c r="L26" s="5" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 3 粒度 · 4 代理键 · 5 分区主键 · 7 缓变维 · 12 索引与检索路径 ｜ 另涉 LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -10101,6 +11391,16 @@
       </c>
       <c r="K27" s="5" t="inlineStr"/>
       <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 3 粒度 · 4 代理键 · 5 分区主键 · 7 缓变维 · 12 索引与检索路径 ｜ 正文引用：LD-02 14</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -10159,6 +11459,16 @@
           <t>v0.2 修订：AI 能力由 AI 包实现，本方提供接口（DD-28）</t>
         </is>
       </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 3 查询 API · 4 记录检索 ｜ LD-05 5 报表与仪表板的机制</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -10213,6 +11523,16 @@
       </c>
       <c r="K29" s="5" t="inlineStr"/>
       <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 3 查询 API · 4 记录检索 ｜ LD-05 5 报表与仪表板的机制</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -10267,6 +11587,16 @@
       </c>
       <c r="K30" s="5" t="inlineStr"/>
       <c r="L30" s="5" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 3 查询 API · 4 记录检索 ｜ LD-05 5 报表与仪表板的机制</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -10321,6 +11651,16 @@
       </c>
       <c r="K31" s="5" t="inlineStr"/>
       <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 3 查询 API · 4 记录检索 ｜ LD-05 5 报表与仪表板的机制 ｜ 正文引用：LD-05 11</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -10375,6 +11715,16 @@
       </c>
       <c r="K32" s="5" t="inlineStr"/>
       <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 3 查询 API · 4 记录检索 ｜ LD-05 5 报表与仪表板的机制 ｜ 另涉 LD-06（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -10429,6 +11779,16 @@
       </c>
       <c r="K33" s="5" t="inlineStr"/>
       <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 3 查询 API · 4 记录检索 ｜ LD-05 5 报表与仪表板的机制</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -10483,6 +11843,16 @@
       </c>
       <c r="K34" s="5" t="inlineStr"/>
       <c r="L34" s="5" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 3 查询 API · 4 记录检索 ｜ LD-05 5 报表与仪表板的机制</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -10537,6 +11907,16 @@
       </c>
       <c r="K35" s="5" t="inlineStr"/>
       <c r="L35" s="5" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 4 元字段呈现 · 5 报表与仪表板的机制 ｜ LD-05A 报表规格（40） ｜ 另涉 LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -10591,6 +11971,16 @@
       </c>
       <c r="K36" s="5" t="inlineStr"/>
       <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 4 元字段呈现 · 5 报表与仪表板的机制 ｜ LD-05A 报表规格（40） ｜ 另涉 LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -10645,6 +12035,16 @@
       </c>
       <c r="K37" s="5" t="inlineStr"/>
       <c r="L37" s="5" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 4 元字段呈现 · 5 报表与仪表板的机制 ｜ LD-05A 报表规格（40）</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -10699,6 +12099,16 @@
       </c>
       <c r="K38" s="5" t="inlineStr"/>
       <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 4 元字段呈现 · 5 报表与仪表板的机制 ｜ LD-05A 报表规格（40） ｜ 另涉 LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -10753,6 +12163,16 @@
       </c>
       <c r="K39" s="5" t="inlineStr"/>
       <c r="L39" s="5" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 4 元字段呈现 · 5 报表与仪表板的机制 ｜ LD-05A 报表规格（40） ｜ 另涉 LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -10807,6 +12227,16 @@
       </c>
       <c r="K40" s="5" t="inlineStr"/>
       <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 4 元字段呈现 · 5 报表与仪表板的机制 ｜ LD-05A 报表规格（40） ｜ 另涉 LD-03 · LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -10865,6 +12295,16 @@
           <t>v0.2 修订：AI 特性由 AI 包提供，本方承担渲染口径与权限（DD-28）</t>
         </is>
       </c>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 4 元字段呈现 · 5 报表与仪表板的机制 ｜ LD-05A 报表规格（40） ｜ 另涉 LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -10919,6 +12359,16 @@
       </c>
       <c r="K42" s="5" t="inlineStr"/>
       <c r="L42" s="5" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 4 元字段呈现 · 5 报表与仪表板的机制 ｜ LD-05A 报表规格（40） ｜ 另涉 LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -10973,6 +12423,16 @@
       </c>
       <c r="K43" s="5" t="inlineStr"/>
       <c r="L43" s="5" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 4 元字段呈现 · 5 报表与仪表板的机制 ｜ LD-05A 报表规格（40） ｜ 正文引用：LD-01 11 ; LD-02 7 ; LD-10 5.5 ｜ 另涉 LD-02 · LD-06（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -11027,6 +12487,16 @@
       </c>
       <c r="K44" s="5" t="inlineStr"/>
       <c r="L44" s="5" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 4 元字段呈现 · 5 报表与仪表板的机制 ｜ LD-05A 报表规格（40） ｜ 另涉 LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -11081,6 +12551,16 @@
       </c>
       <c r="K45" s="5" t="inlineStr"/>
       <c r="L45" s="5" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 5 机制 · 6 地图嵌入 · 7 指挥大屏 ｜ LD-05A 仪表板规格（20）</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -11135,6 +12615,16 @@
       </c>
       <c r="K46" s="5" t="inlineStr"/>
       <c r="L46" s="5" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 5 机制 · 6 地图嵌入 · 7 指挥大屏 ｜ LD-05A 仪表板规格（20） ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -11189,6 +12679,16 @@
       </c>
       <c r="K47" s="5" t="inlineStr"/>
       <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 5 机制 · 6 地图嵌入 · 7 指挥大屏 ｜ LD-05A 仪表板规格（20） ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -11243,6 +12743,16 @@
       </c>
       <c r="K48" s="5" t="inlineStr"/>
       <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 5 机制 · 6 地图嵌入 · 7 指挥大屏 ｜ LD-05A 仪表板规格（20） ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -11297,6 +12807,16 @@
       </c>
       <c r="K49" s="5" t="inlineStr"/>
       <c r="L49" s="5" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 5 机制 · 6 地图嵌入 · 7 指挥大屏 ｜ LD-05A 仪表板规格（20）</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -11351,6 +12871,16 @@
       </c>
       <c r="K50" s="5" t="inlineStr"/>
       <c r="L50" s="5" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 5 机制 · 6 地图嵌入 · 7 指挥大屏 ｜ LD-05A 仪表板规格（20）</t>
+        </is>
+      </c>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -11405,6 +12935,16 @@
       </c>
       <c r="K51" s="5" t="inlineStr"/>
       <c r="L51" s="5" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 5 机制 · 6 地图嵌入 · 7 指挥大屏 ｜ LD-05A 仪表板规格（20）</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -11459,6 +12999,16 @@
       </c>
       <c r="K52" s="5" t="inlineStr"/>
       <c r="L52" s="5" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 5 机制 · 6 地图嵌入 · 7 指挥大屏 ｜ LD-05A 仪表板规格（20） ｜ 另涉 LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -11513,6 +13063,16 @@
       </c>
       <c r="K53" s="5" t="inlineStr"/>
       <c r="L53" s="5" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 5 机制 · 6 地图嵌入 · 7 指挥大屏 ｜ LD-05A 仪表板规格（20）</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -11571,6 +13131,16 @@
           <t>v0.2 修订：空间聚合在本方 mart 层（PostGIS），呈现用 HudHud 嵌入式组件（CN-29 · CN-32）</t>
         </is>
       </c>
+      <c r="M54" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 5 机制 · 6 地图嵌入 · 7 指挥大屏 ｜ LD-05A 仪表板规格（20） ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N54" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -11625,6 +13195,16 @@
       </c>
       <c r="K55" s="5" t="inlineStr"/>
       <c r="L55" s="5" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>LD-05 5 机制 · 6 地图嵌入 · 7 指挥大屏 ｜ LD-05A 仪表板规格（20） ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -11679,6 +13259,16 @@
       </c>
       <c r="K56" s="5" t="inlineStr"/>
       <c r="L56" s="5" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 7 对外数据服务与 ESB · 8 AI 集成的四个接口</t>
+        </is>
+      </c>
+      <c r="N56" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -11733,6 +13323,16 @@
       </c>
       <c r="K57" s="5" t="inlineStr"/>
       <c r="L57" s="5" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 7 对外数据服务与 ESB · 8 AI 集成的四个接口</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -11787,6 +13387,16 @@
       </c>
       <c r="K58" s="5" t="inlineStr"/>
       <c r="L58" s="5" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 7 对外数据服务与 ESB · 8 AI 集成的四个接口</t>
+        </is>
+      </c>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
@@ -11841,6 +13451,16 @@
       </c>
       <c r="K59" s="5" t="inlineStr"/>
       <c r="L59" s="5" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 7 对外数据服务与 ESB · 8 AI 集成的四个接口 ｜ 另涉 LD-06（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
@@ -11899,6 +13519,16 @@
           <t>v0.2 修订：本期交付，实质差异消解（DD-30）</t>
         </is>
       </c>
+      <c r="M60" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 9 移动端对外面 ｜ LD-05 8 移动端</t>
+        </is>
+      </c>
+      <c r="N60" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -11953,6 +13583,16 @@
       </c>
       <c r="K61" s="5" t="inlineStr"/>
       <c r="L61" s="5" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -12007,6 +13647,16 @@
       </c>
       <c r="K62" s="5" t="inlineStr"/>
       <c r="L62" s="5" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理</t>
+        </is>
+      </c>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -12061,6 +13711,16 @@
       </c>
       <c r="K63" s="5" t="inlineStr"/>
       <c r="L63" s="5" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -12115,6 +13775,16 @@
       </c>
       <c r="K64" s="5" t="inlineStr"/>
       <c r="L64" s="5" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-01 · LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -12169,6 +13839,16 @@
       </c>
       <c r="K65" s="5" t="inlineStr"/>
       <c r="L65" s="5" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -12223,6 +13903,16 @@
       </c>
       <c r="K66" s="5" t="inlineStr"/>
       <c r="L66" s="5" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份联邦与令牌 · 7 审计 ｜ 另涉 LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
@@ -12277,6 +13967,16 @@
       </c>
       <c r="K67" s="5" t="inlineStr"/>
       <c r="L67" s="5" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份联邦与令牌 · 7 审计 ｜ 另涉 LD-04 · LD-06（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N67" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
@@ -12335,6 +14035,16 @@
           <t>v0.2 修订：优先级由「预留」改为「必须」，改为按派驻部门的行级安全（AS-14 已推翻 · DD-41）</t>
         </is>
       </c>
+      <c r="M68" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份联邦与令牌 · 7 审计 ｜ 另涉 LD-03 · LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
@@ -12389,6 +14099,16 @@
       </c>
       <c r="K69" s="5" t="inlineStr"/>
       <c r="L69" s="5" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份联邦与令牌 · 7 审计 ｜ 正文引用：LD-10 6 ｜ 另涉 LD-02 · LD-08（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N69" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
@@ -12443,6 +14163,16 @@
       </c>
       <c r="K70" s="5" t="inlineStr"/>
       <c r="L70" s="5" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份联邦与令牌 · 7 审计 ｜ 另涉 LD-02 · LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
@@ -12497,6 +14227,16 @@
       </c>
       <c r="K71" s="5" t="inlineStr"/>
       <c r="L71" s="5" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份联邦与令牌 · 7 审计 ｜ 正文引用：LD-05 6.2 ｜ 另涉 LD-06（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N71" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
@@ -12551,6 +14291,16 @@
       </c>
       <c r="K72" s="5" t="inlineStr"/>
       <c r="L72" s="5" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr">
+        <is>
+          <t>LD-08 2 按日考核 · 3 集群结构 · 4 RPO/RTO 与降级决策树 · 10 服务水平举证 ｜ 另涉 LD-02 · LD-06（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
@@ -12605,6 +14355,16 @@
       </c>
       <c r="K73" s="5" t="inlineStr"/>
       <c r="L73" s="5" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr">
+        <is>
+          <t>LD-08 2 按日考核 · 3 集群结构 · 4 RPO/RTO 与降级决策树 · 10 服务水平举证 ｜ 正文引用：LD-10 9 ｜ 另涉 LD-02（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N73" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
@@ -12659,6 +14419,16 @@
       </c>
       <c r="K74" s="5" t="inlineStr"/>
       <c r="L74" s="5" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr">
+        <is>
+          <t>LD-08 2 按日考核 · 3 集群结构 · 4 RPO/RTO 与降级决策树 · 10 服务水平举证 ｜ 正文引用：LD-10 9</t>
+        </is>
+      </c>
+      <c r="N74" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
@@ -12713,6 +14483,16 @@
       </c>
       <c r="K75" s="5" t="inlineStr"/>
       <c r="L75" s="5" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr">
+        <is>
+          <t>LD-08 2 按日考核 · 3 集群结构 · 4 RPO/RTO 与降级决策树 · 10 服务水平举证 ｜ 另涉 LD-06（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -12771,6 +14551,16 @@
           <t>v0.2 修订：响应时间改为三档分层（DD-36）</t>
         </is>
       </c>
+      <c r="M76" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 3 查询 API（保护措施与三档路径） ｜ LD-05 9 渲染预算 ｜ 另涉 LD-02（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N76" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
@@ -12825,6 +14615,16 @@
       </c>
       <c r="K77" s="5" t="inlineStr"/>
       <c r="L77" s="5" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 3 查询 API（保护措施与三档路径） ｜ LD-05 9 渲染预算</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -12879,6 +14679,16 @@
       </c>
       <c r="K78" s="5" t="inlineStr"/>
       <c r="L78" s="5" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 3 查询 API（保护措施与三档路径） ｜ LD-05 9 渲染预算 ｜ 正文引用：LD-09 10 ｜ 另涉 LD-02（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N78" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
@@ -12937,6 +14747,16 @@
           <t>v0.2 修订：管理界面十个改为十一个（DD-40）</t>
         </is>
       </c>
+      <c r="M79" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 2 共同规则 · 3 接入与数据质量 · 6 平台运行 · 7 危险动作清单 ｜ LD-08 7 发布与回滚</t>
+        </is>
+      </c>
+      <c r="N79" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
@@ -12991,6 +14811,16 @@
       </c>
       <c r="K80" s="5" t="inlineStr"/>
       <c r="L80" s="5" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 2 共同规则 · 3 接入与数据质量 · 6 平台运行 · 7 危险动作清单 ｜ LD-08 7 发布与回滚</t>
+        </is>
+      </c>
+      <c r="N80" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
@@ -13045,6 +14875,16 @@
       </c>
       <c r="K81" s="5" t="inlineStr"/>
       <c r="L81" s="5" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 2 共同规则 · 3 接入与数据质量 · 6 平台运行 · 7 危险动作清单 ｜ LD-08 7 发布与回滚 ｜ 另涉 LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N81" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
@@ -13099,6 +14939,16 @@
       </c>
       <c r="K82" s="5" t="inlineStr"/>
       <c r="L82" s="5" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr">
+        <is>
+          <t>LD-06 2 共同规则 · 3 接入与数据质量 · 6 平台运行 · 7 危险动作清单 ｜ LD-08 7 发布与回滚 ｜ 另涉 LD-01（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N82" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
@@ -13153,6 +15003,16 @@
       </c>
       <c r="K83" s="5" t="inlineStr"/>
       <c r="L83" s="5" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr">
+        <is>
+          <t>LD-08 5 备份与恢复 ｜ LD-02 9 raw 与 staging（保留与分区） ｜ 正文引用：LD-10 9</t>
+        </is>
+      </c>
+      <c r="N83" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
@@ -13207,6 +15067,16 @@
       </c>
       <c r="K84" s="5" t="inlineStr"/>
       <c r="L84" s="5" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr">
+        <is>
+          <t>LD-08 5 备份与恢复 ｜ LD-02 9 raw 与 staging（保留与分区）</t>
+        </is>
+      </c>
+      <c r="N84" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -13261,6 +15131,16 @@
       </c>
       <c r="K85" s="5" t="inlineStr"/>
       <c r="L85" s="5" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr">
+        <is>
+          <t>LD-08 5 备份与恢复 ｜ LD-02 9 raw 与 staging（保留与分区） ｜ 另涉 LD-06（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N85" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
@@ -13319,6 +15199,16 @@
           <t>v0.2 修订：保留期改为三层，纠正八年在线的口径误读（DD-38）</t>
         </is>
       </c>
+      <c r="M86" s="7" t="inlineStr">
+        <is>
+          <t>LD-08 5 备份与恢复 ｜ LD-02 9 raw 与 staging（保留与分区）</t>
+        </is>
+      </c>
+      <c r="N86" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
@@ -13373,6 +15263,16 @@
       </c>
       <c r="K87" s="5" t="inlineStr"/>
       <c r="L87" s="5" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr">
+        <is>
+          <t>LD-09 3 组件与版本清单 · 4 许可判定与传染性 · 5 上市年限举证 · 6 许可条件与部署自由度 ｜ 正文引用：LD-02 14</t>
+        </is>
+      </c>
+      <c r="N87" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
@@ -13427,6 +15327,16 @@
       </c>
       <c r="K88" s="5" t="inlineStr"/>
       <c r="L88" s="5" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr">
+        <is>
+          <t>LD-09 3 组件与版本清单 · 4 许可判定与传染性 · 5 上市年限举证 · 6 许可条件与部署自由度</t>
+        </is>
+      </c>
+      <c r="N88" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
@@ -13481,6 +15391,16 @@
       </c>
       <c r="K89" s="5" t="inlineStr"/>
       <c r="L89" s="5" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 2 业务对象模型（站点维度）· 4 代理键 ｜ LD-08 9.2 两个机架的固有约束 ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
@@ -13535,6 +15455,16 @@
       </c>
       <c r="K90" s="5" t="inlineStr"/>
       <c r="L90" s="5" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 2 业务对象模型（站点维度）· 4 代理键 ｜ LD-08 9.2 两个机架的固有约束</t>
+        </is>
+      </c>
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
@@ -13589,6 +15519,16 @@
       </c>
       <c r="K91" s="5" t="inlineStr"/>
       <c r="L91" s="5" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 2 业务对象模型（站点维度）· 4 代理键 ｜ LD-08 9.2 两个机架的固有约束 ｜ 另涉 LD-01（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N91" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
@@ -13643,6 +15583,16 @@
       </c>
       <c r="K92" s="5" t="inlineStr"/>
       <c r="L92" s="5" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 2 业务对象模型（站点维度）· 4 代理键 ｜ LD-08 9.2 两个机架的固有约束 ｜ 另涉 LD-06（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N92" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
@@ -13697,6 +15647,16 @@
       </c>
       <c r="K93" s="5" t="inlineStr"/>
       <c r="L93" s="5" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr">
+        <is>
+          <t>LD-00 文档索引 ｜ 各册「交付物」一章 ｜ 正文引用：LD-02 14</t>
+        </is>
+      </c>
+      <c r="N93" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
@@ -13751,6 +15711,16 @@
       </c>
       <c r="K94" s="5" t="inlineStr"/>
       <c r="L94" s="5" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr">
+        <is>
+          <t>LD-00 文档索引 ｜ 各册「交付物」一章 ｜ 另涉 LD-05（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N94" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
@@ -13805,6 +15775,16 @@
       </c>
       <c r="K95" s="5" t="inlineStr"/>
       <c r="L95" s="5" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>LD-00 文档索引 ｜ 各册「交付物」一章 ｜ 另涉 LD-02 · LD-05（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
@@ -13859,6 +15839,16 @@
       </c>
       <c r="K96" s="5" t="inlineStr"/>
       <c r="L96" s="5" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr">
+        <is>
+          <t>LD-00 文档索引 ｜ 各册「交付物」一章</t>
+        </is>
+      </c>
+      <c r="N96" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
@@ -13913,6 +15903,16 @@
       </c>
       <c r="K97" s="5" t="inlineStr"/>
       <c r="L97" s="5" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr">
+        <is>
+          <t>LD-00 文档索引 ｜ 各册「交付物」一章 ｜ 另涉 LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N97" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
@@ -13967,6 +15967,16 @@
       </c>
       <c r="K98" s="5" t="inlineStr"/>
       <c r="L98" s="5" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr">
+        <is>
+          <t>LD-00 文档索引 ｜ 各册「交付物」一章 ｜ 正文引用：LD-02 14 ｜ 另涉 LD-09（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N98" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
@@ -14021,6 +16031,16 @@
       </c>
       <c r="K99" s="5" t="inlineStr"/>
       <c r="L99" s="5" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 6 归档迁移 · 8 对账</t>
+        </is>
+      </c>
+      <c r="N99" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
@@ -14075,6 +16095,16 @@
       </c>
       <c r="K100" s="5" t="inlineStr"/>
       <c r="L100" s="5" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 6 归档迁移 · 8 对账</t>
+        </is>
+      </c>
+      <c r="N100" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
@@ -14129,6 +16159,16 @@
       </c>
       <c r="K101" s="5" t="inlineStr"/>
       <c r="L101" s="5" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 6 归档迁移 · 8 对账 ｜ 另涉 LD-02（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N101" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
@@ -14183,6 +16223,16 @@
       </c>
       <c r="K102" s="5" t="inlineStr"/>
       <c r="L102" s="5" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 6 归档迁移 · 8 对账 ｜ 正文引用：LD-01 6.3 ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N102" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
@@ -14237,6 +16287,16 @@
       </c>
       <c r="K103" s="5" t="inlineStr"/>
       <c r="L103" s="5" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 6 归档迁移 · 8 对账</t>
+        </is>
+      </c>
+      <c r="N103" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
@@ -14291,6 +16351,16 @@
       </c>
       <c r="K104" s="5" t="inlineStr"/>
       <c r="L104" s="5" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 6 归档迁移 · 8 对账</t>
+        </is>
+      </c>
+      <c r="N104" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
@@ -14345,6 +16415,16 @@
       </c>
       <c r="K105" s="5" t="inlineStr"/>
       <c r="L105" s="5" t="inlineStr"/>
+      <c r="M105" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 6 归档迁移 · 8 对账 ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N105" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
@@ -14399,6 +16479,16 @@
       </c>
       <c r="K106" s="5" t="inlineStr"/>
       <c r="L106" s="5" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 6 归档迁移 · 8 对账 ｜ 另涉 LD-10（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N106" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
@@ -14453,6 +16543,16 @@
       </c>
       <c r="K107" s="5" t="inlineStr"/>
       <c r="L107" s="5" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr">
+        <is>
+          <t>LD-01 6 归档迁移 · 8 对账</t>
+        </is>
+      </c>
+      <c r="N107" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
@@ -14507,6 +16607,16 @@
       </c>
       <c r="K108" s="5" t="inlineStr"/>
       <c r="L108" s="5" t="inlineStr"/>
+      <c r="M108" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 正文引用：LD-06 5.3 ; LD-07 11</t>
+        </is>
+      </c>
+      <c r="N108" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
@@ -14561,6 +16671,16 @@
       </c>
       <c r="K109" s="5" t="inlineStr"/>
       <c r="L109" s="5" t="inlineStr"/>
+      <c r="M109" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N109" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
@@ -14619,6 +16739,16 @@
           <t>v0.2 修订：归 M-11，扫描周期可配置（DD-40）</t>
         </is>
       </c>
+      <c r="M110" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N110" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
@@ -14673,6 +16803,16 @@
       </c>
       <c r="K111" s="5" t="inlineStr"/>
       <c r="L111" s="5" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-02 · LD-03（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N111" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
@@ -14731,6 +16871,16 @@
           <t>v0.2 修订：端到端压测，首屏与交互分开统计（DD-36）</t>
         </is>
       </c>
+      <c r="M112" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 3 查询 API（保护措施与三档路径） ｜ LD-05 9 渲染预算 ｜ 另涉 LD-10（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N112" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
@@ -14785,6 +16935,16 @@
       </c>
       <c r="K113" s="5" t="inlineStr"/>
       <c r="L113" s="5" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 3 查询 API（保护措施与三档路径） ｜ LD-05 9 渲染预算 ｜ 另涉 LD-03 · LD-06（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N113" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
@@ -14839,6 +16999,16 @@
       </c>
       <c r="K114" s="5" t="inlineStr"/>
       <c r="L114" s="5" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr">
+        <is>
+          <t>LD-09 3 组件与版本清单 · 4 许可判定与传染性 · 5 上市年限举证 · 6 许可条件与部署自由度</t>
+        </is>
+      </c>
+      <c r="N114" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
@@ -14893,6 +17063,16 @@
       </c>
       <c r="K115" s="5" t="inlineStr"/>
       <c r="L115" s="5" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr">
+        <is>
+          <t>LD-09 3 组件与版本清单 · 4 许可判定与传染性 · 5 上市年限举证 · 6 许可条件与部署自由度 ｜ 另涉 LD-06（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N115" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
@@ -14947,6 +17127,16 @@
       </c>
       <c r="K116" s="5" t="inlineStr"/>
       <c r="L116" s="5" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr">
+        <is>
+          <t>LD-09 3 组件与版本清单 · 4 许可判定与传染性 · 5 上市年限举证 · 6 许可条件与部署自由度 ｜ 另涉 LD-02（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N116" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
@@ -15001,6 +17191,16 @@
       </c>
       <c r="K117" s="5" t="inlineStr"/>
       <c r="L117" s="5" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr">
+        <is>
+          <t>LD-09 3 组件与版本清单 · 4 许可判定与传染性 · 5 上市年限举证 · 6 许可条件与部署自由度</t>
+        </is>
+      </c>
+      <c r="N117" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
@@ -15055,6 +17255,16 @@
       </c>
       <c r="K118" s="5" t="inlineStr"/>
       <c r="L118" s="5" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr">
+        <is>
+          <t>LD-09 3 组件与版本清单 · 4 许可判定与传染性 · 5 上市年限举证 · 6 许可条件与部署自由度 ｜ 正文引用：LD-09 6.1 ｜ 另涉 LD-06（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N118" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
@@ -15109,6 +17319,16 @@
       </c>
       <c r="K119" s="5" t="inlineStr"/>
       <c r="L119" s="5" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr">
+        <is>
+          <t>LD-09 3 组件与版本清单 · 4 许可判定与传染性 · 5 上市年限举证 · 6 许可条件与部署自由度 ｜ 正文引用：LD-09 10 ; LD-09 3 ; LD-09 7 ｜ 另涉 LD-06 · LD-08（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N119" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + LD 正文显式引用 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
@@ -15167,6 +17387,16 @@
           <t>v0.2 修订：资源数据经 CAD 取得，不新增数据源（DD-42）</t>
         </is>
       </c>
+      <c r="M120" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 3 粒度 · 4 代理键 · 5 分区主键 · 7 缓变维 · 12 索引与检索路径 ｜ 另涉 LD-01 · LD-04（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N120" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
@@ -15221,6 +17451,16 @@
       </c>
       <c r="K121" s="5" t="inlineStr"/>
       <c r="L121" s="5" t="inlineStr"/>
+      <c r="M121" s="7" t="inlineStr">
+        <is>
+          <t>LD-02 3 粒度 · 4 代理键 · 5 分区主键 · 7 缓变维 · 12 索引与检索路径 ｜ 另涉 LD-06（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N121" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
@@ -15279,6 +17519,16 @@
           <t>v0.2 新增（DD-34）</t>
         </is>
       </c>
+      <c r="M122" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 3 查询 API · 4 记录检索 ｜ LD-05 5 报表与仪表板的机制</t>
+        </is>
+      </c>
+      <c r="N122" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
@@ -15337,6 +17587,16 @@
           <t>v0.2 新增（DD-28 · DD-29）</t>
         </is>
       </c>
+      <c r="M123" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 7 对外数据服务与 ESB · 8 AI 集成的四个接口</t>
+        </is>
+      </c>
+      <c r="N123" s="7" t="inlineStr">
+        <is>
+          <t>领域主章</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
@@ -15395,6 +17655,16 @@
           <t>v0.2 新增（DD-28）</t>
         </is>
       </c>
+      <c r="M124" s="7" t="inlineStr">
+        <is>
+          <t>LD-04 7 对外数据服务与 ESB · 8 AI 集成的四个接口 ｜ 另涉 LD-01（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N124" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
@@ -15451,6 +17721,16 @@
       <c r="L125" s="5" t="inlineStr">
         <is>
           <t>v0.2 新增（DD-35）</t>
+        </is>
+      </c>
+      <c r="M125" s="7" t="inlineStr">
+        <is>
+          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份联邦与令牌 · 7 审计 ｜ 另涉 LD-04 · LD-06（按责任组件）</t>
+        </is>
+      </c>
+      <c r="N125" s="7" t="inlineStr">
+        <is>
+          <t>领域主章 + 责任组件</t>
         </is>
       </c>
     </row>
@@ -15580,7 +17860,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>已覆盖：R-13 · M-I09（REQ-RPT-01）</t>
+          <t>已覆盖：R-13 · M-I06 · M-I22 · M-I23（REQ-RPT-01）（原 M-I09 已按 LD-03 拆为均值、中位、P90 三个指标）</t>
         </is>
       </c>
     </row>

--- a/HD-02_需求追溯矩阵.xlsx
+++ b/HD-02_需求追溯矩阵.xlsx
@@ -570,6 +570,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
@@ -13585,7 +13586,7 @@
       <c r="L61" s="5" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理</t>
+          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
@@ -13649,7 +13650,7 @@
       <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理</t>
+          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
@@ -13713,7 +13714,7 @@
       <c r="L63" s="5" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理</t>
+          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
@@ -13777,7 +13778,7 @@
       <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-01 · LD-03（按责任组件）</t>
+          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-01 · LD-03（按责任组件）</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
@@ -13841,7 +13842,7 @@
       <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-04（按责任组件）</t>
+          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-04（按责任组件）</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
@@ -13905,7 +13906,7 @@
       <c r="L66" s="5" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr">
         <is>
-          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份联邦与令牌 · 7 审计 ｜ 另涉 LD-04（按责任组件）</t>
+          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份（经 AD FS 代理） · 8 审计 ｜ 另涉 LD-04（按责任组件）</t>
         </is>
       </c>
       <c r="N66" s="7" t="inlineStr">
@@ -13969,7 +13970,7 @@
       <c r="L67" s="5" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr">
         <is>
-          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份联邦与令牌 · 7 审计 ｜ 另涉 LD-04 · LD-06（按责任组件）</t>
+          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份（经 AD FS 代理） · 8 审计 ｜ 另涉 LD-04 · LD-06（按责任组件）</t>
         </is>
       </c>
       <c r="N67" s="7" t="inlineStr">
@@ -14037,7 +14038,7 @@
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份联邦与令牌 · 7 审计 ｜ 另涉 LD-03 · LD-04（按责任组件）</t>
+          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份（经 AD FS 代理） · 8 审计 ｜ 另涉 LD-03 · LD-04（按责任组件）</t>
         </is>
       </c>
       <c r="N68" s="7" t="inlineStr">
@@ -14101,7 +14102,7 @@
       <c r="L69" s="5" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份联邦与令牌 · 7 审计 ｜ 正文引用：LD-10 6 ｜ 另涉 LD-02 · LD-08（按责任组件）</t>
+          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份（经 AD FS 代理） · 8 审计 ｜ 正文引用：LD-10 6 ｜ 另涉 LD-02 · LD-08（按责任组件）</t>
         </is>
       </c>
       <c r="N69" s="7" t="inlineStr">
@@ -14165,7 +14166,7 @@
       <c r="L70" s="5" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份联邦与令牌 · 7 审计 ｜ 另涉 LD-02 · LD-04（按责任组件）</t>
+          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份（经 AD FS 代理） · 8 审计 ｜ 另涉 LD-02 · LD-04（按责任组件）</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
@@ -14229,7 +14230,7 @@
       <c r="L71" s="5" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份联邦与令牌 · 7 审计 ｜ 正文引用：LD-05 6.2 ｜ 另涉 LD-06（按责任组件）</t>
+          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份（经 AD FS 代理） · 8 审计 ｜ 正文引用：LD-05 6.2 ｜ 另涉 LD-06（按责任组件）</t>
         </is>
       </c>
       <c r="N71" s="7" t="inlineStr">
@@ -16609,7 +16610,7 @@
       <c r="L108" s="5" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr">
         <is>
-          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 正文引用：LD-06 5.3 ; LD-07 11</t>
+          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 正文引用：LD-06 5.3 ; LD-07 11</t>
         </is>
       </c>
       <c r="N108" s="7" t="inlineStr">
@@ -16673,7 +16674,7 @@
       <c r="L109" s="5" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr">
         <is>
-          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-03（按责任组件）</t>
+          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-03（按责任组件）</t>
         </is>
       </c>
       <c r="N109" s="7" t="inlineStr">
@@ -16741,7 +16742,7 @@
       </c>
       <c r="M110" s="7" t="inlineStr">
         <is>
-          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-03（按责任组件）</t>
+          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-03（按责任组件）</t>
         </is>
       </c>
       <c r="N110" s="7" t="inlineStr">
@@ -16805,7 +16806,7 @@
       <c r="L111" s="5" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr">
         <is>
-          <t>LD-07 8 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-02 · LD-03（按责任组件）</t>
+          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-02 · LD-03（按责任组件）</t>
         </is>
       </c>
       <c r="N111" s="7" t="inlineStr">
@@ -17725,7 +17726,7 @@
       </c>
       <c r="M125" s="7" t="inlineStr">
         <is>
-          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份联邦与令牌 · 7 审计 ｜ 另涉 LD-04 · LD-06（按责任组件）</t>
+          <t>LD-07 2 三层权限 · 3 出口路径×权限层 · 5 受控 SQL 授权 · 6 身份（经 AD FS 代理） · 8 审计 ｜ 另涉 LD-04 · LD-06（按责任组件）</t>
         </is>
       </c>
       <c r="N125" s="7" t="inlineStr">

--- a/HD-02_需求追溯矩阵.xlsx
+++ b/HD-02_需求追溯矩阵.xlsx
@@ -13586,7 +13586,7 @@
       <c r="L61" s="5" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr">
         <is>
-          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理</t>
+          <t>LD-07 9 脱敏与匿名化 · 10 两项前置门 ｜ LD-06 5 安全、审计与治理</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
@@ -13650,7 +13650,7 @@
       <c r="L62" s="5" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr">
         <is>
-          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理</t>
+          <t>LD-07 9 脱敏与匿名化 · 10 两项前置门 ｜ LD-06 5 安全、审计与治理</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
@@ -13714,7 +13714,7 @@
       <c r="L63" s="5" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr">
         <is>
-          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理</t>
+          <t>LD-07 9 脱敏与匿名化 · 10 两项前置门 ｜ LD-06 5 安全、审计与治理</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
@@ -13778,7 +13778,7 @@
       <c r="L64" s="5" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr">
         <is>
-          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-01 · LD-03（按责任组件）</t>
+          <t>LD-07 9 脱敏与匿名化 · 10 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-01 · LD-03（按责任组件）</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
@@ -13842,7 +13842,7 @@
       <c r="L65" s="5" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr">
         <is>
-          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-04（按责任组件）</t>
+          <t>LD-07 9 脱敏与匿名化 · 10 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-04（按责任组件）</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
@@ -16610,7 +16610,7 @@
       <c r="L108" s="5" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr">
         <is>
-          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 正文引用：LD-06 5.3 ; LD-07 11</t>
+          <t>LD-07 9 脱敏与匿名化 · 10 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 正文引用：LD-06 5.3 ; LD-07 11</t>
         </is>
       </c>
       <c r="N108" s="7" t="inlineStr">
@@ -16674,7 +16674,7 @@
       <c r="L109" s="5" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr">
         <is>
-          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-03（按责任组件）</t>
+          <t>LD-07 9 脱敏与匿名化 · 10 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-03（按责任组件）</t>
         </is>
       </c>
       <c r="N109" s="7" t="inlineStr">
@@ -16742,7 +16742,7 @@
       </c>
       <c r="M110" s="7" t="inlineStr">
         <is>
-          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-03（按责任组件）</t>
+          <t>LD-07 9 脱敏与匿名化 · 10 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-03（按责任组件）</t>
         </is>
       </c>
       <c r="N110" s="7" t="inlineStr">
@@ -16806,7 +16806,7 @@
       <c r="L111" s="5" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr">
         <is>
-          <t>LD-07 9 脱敏与匿名化 · 9 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-02 · LD-03（按责任组件）</t>
+          <t>LD-07 9 脱敏与匿名化 · 10 两项前置门 ｜ LD-06 5 安全、审计与治理 ｜ 另涉 LD-02 · LD-03（按责任组件）</t>
         </is>
       </c>
       <c r="N111" s="7" t="inlineStr">

--- a/HD-02_需求追溯矩阵.xlsx
+++ b/HD-02_需求追溯矩阵.xlsx
@@ -10106,7 +10106,7 @@
       <c r="L7" s="5" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr">
         <is>
-          <t>LD-02 2 业务对象模型 · 9 raw 与 staging · 11 meta 与 audit ｜ 正文引用：LD-02 14 ; LD-04 12</t>
+          <t>LD-02 2 业务对象模型 · 9 raw 与 staging · 11 meta 与 audit ｜ 正文引用：LD-02 15 ; LD-04 12</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
@@ -11202,7 +11202,7 @@
       <c r="L24" s="5" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr">
         <is>
-          <t>LD-02 3 粒度 · 4 代理键 · 5 分区主键 · 7 缓变维 · 12 索引与检索路径 ｜ 正文引用：LD-02 14 ｜ 另涉 LD-03（按责任组件）</t>
+          <t>LD-02 3 粒度 · 4 代理键 · 5 分区主键 · 7 缓变维 · 12 索引与检索路径 ｜ 正文引用：LD-02 15 ｜ 另涉 LD-03（按责任组件）</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
@@ -11394,7 +11394,7 @@
       <c r="L27" s="5" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr">
         <is>
-          <t>LD-02 3 粒度 · 4 代理键 · 5 分区主键 · 7 缓变维 · 12 索引与检索路径 ｜ 正文引用：LD-02 14</t>
+          <t>LD-02 3 粒度 · 4 代理键 · 5 分区主键 · 7 缓变维 · 12 索引与检索路径 ｜ 正文引用：LD-02 15</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
@@ -15266,7 +15266,7 @@
       <c r="L87" s="5" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>LD-09 3 组件与版本清单 · 4 许可判定与传染性 · 5 上市年限举证 · 6 许可条件与部署自由度 ｜ 正文引用：LD-02 14</t>
+          <t>LD-09 3 组件与版本清单 · 4 许可判定与传染性 · 5 上市年限举证 · 6 许可条件与部署自由度 ｜ 正文引用：LD-02 15</t>
         </is>
       </c>
       <c r="N87" s="7" t="inlineStr">
@@ -15650,7 +15650,7 @@
       <c r="L93" s="5" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr">
         <is>
-          <t>LD-00 文档索引 ｜ 各册「交付物」一章 ｜ 正文引用：LD-02 14</t>
+          <t>LD-00 文档索引 ｜ 各册「交付物」一章 ｜ 正文引用：LD-02 15</t>
         </is>
       </c>
       <c r="N93" s="7" t="inlineStr">
@@ -15970,7 +15970,7 @@
       <c r="L98" s="5" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr">
         <is>
-          <t>LD-00 文档索引 ｜ 各册「交付物」一章 ｜ 正文引用：LD-02 14 ｜ 另涉 LD-09（按责任组件）</t>
+          <t>LD-00 文档索引 ｜ 各册「交付物」一章 ｜ 正文引用：LD-02 15 ｜ 另涉 LD-09（按责任组件）</t>
         </is>
       </c>
       <c r="N98" s="7" t="inlineStr">

--- a/HD-02_需求追溯矩阵.xlsx
+++ b/HD-02_需求追溯矩阵.xlsx
@@ -11234,7 +11234,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>按天分区，业务数据在线保留八年，raw 层按合同期保留，audit 按合规要求保留。</t>
+          <t>按月分区，业务数据在线保留八年，raw 层按合同期保留，audit 按合规要求保留。</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
